--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/116.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/116.xlsx
@@ -426,13 +426,13 @@
         <v>-15.40576139398037</v>
       </c>
       <c r="E2">
-        <v>-15.25701518169603</v>
+        <v>-15.95025209668623</v>
       </c>
       <c r="F2">
-        <v>-4.202229286746133</v>
+        <v>-5.136029635839155</v>
       </c>
       <c r="G2">
-        <v>-11.82185002340295</v>
+        <v>-12.13481906704903</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.7966884880077</v>
       </c>
       <c r="E3">
-        <v>-16.00775918810964</v>
+        <v>-16.268920812606</v>
       </c>
       <c r="F3">
-        <v>-4.251342361690714</v>
+        <v>-5.031864091671923</v>
       </c>
       <c r="G3">
-        <v>-12.15303037806056</v>
+        <v>-12.03937603915184</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.28275135243171</v>
       </c>
       <c r="E4">
-        <v>-15.17431618936795</v>
+        <v>-16.18929212565512</v>
       </c>
       <c r="F4">
-        <v>-4.041521040398613</v>
+        <v>-4.664539477513732</v>
       </c>
       <c r="G4">
-        <v>-11.0594744228008</v>
+        <v>-12.21314657450818</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.78542390174702</v>
       </c>
       <c r="E5">
-        <v>-16.54438335801858</v>
+        <v>-17.52269676873965</v>
       </c>
       <c r="F5">
-        <v>-4.289312238332835</v>
+        <v>-4.440795785282781</v>
       </c>
       <c r="G5">
-        <v>-10.79873916667334</v>
+        <v>-11.90060128069113</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.28358275812422</v>
       </c>
       <c r="E6">
-        <v>-17.46361376836158</v>
+        <v>-18.10969568350991</v>
       </c>
       <c r="F6">
-        <v>-4.389609306728993</v>
+        <v>-4.595697176136676</v>
       </c>
       <c r="G6">
-        <v>-10.89018967665017</v>
+        <v>-11.41027307032414</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.71143589700372</v>
       </c>
       <c r="E7">
-        <v>-16.83891983595147</v>
+        <v>-17.87850802847032</v>
       </c>
       <c r="F7">
-        <v>-3.794705659264889</v>
+        <v>-4.725744231436977</v>
       </c>
       <c r="G7">
-        <v>-11.50389860872026</v>
+        <v>-12.05123441327351</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.04123492671689</v>
       </c>
       <c r="E8">
-        <v>-17.66838683451442</v>
+        <v>-18.40378384251604</v>
       </c>
       <c r="F8">
-        <v>-4.204755807324672</v>
+        <v>-4.526535953309543</v>
       </c>
       <c r="G8">
-        <v>-11.95516238172386</v>
+        <v>-11.4527738539573</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-18.24188211638379</v>
       </c>
       <c r="E9">
-        <v>-18.87323715746921</v>
+        <v>-20.03960450830681</v>
       </c>
       <c r="F9">
-        <v>-3.389909845641063</v>
+        <v>-3.965481054658632</v>
       </c>
       <c r="G9">
-        <v>-10.16766642324977</v>
+        <v>-11.17211573477451</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.27234113620083</v>
       </c>
       <c r="E10">
-        <v>-20.62471957788988</v>
+        <v>-19.05045898775938</v>
       </c>
       <c r="F10">
-        <v>-4.041145789965145</v>
+        <v>-3.963419248193064</v>
       </c>
       <c r="G10">
-        <v>-10.55967805219149</v>
+        <v>-11.9312668640214</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-18.12576231218923</v>
       </c>
       <c r="E11">
-        <v>-20.44533313702403</v>
+        <v>-20.25025553372161</v>
       </c>
       <c r="F11">
-        <v>-3.423295537076092</v>
+        <v>-3.869651371665772</v>
       </c>
       <c r="G11">
-        <v>-10.73765960147379</v>
+        <v>-11.65888510868678</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-17.79892351209702</v>
       </c>
       <c r="E12">
-        <v>-19.50951039791693</v>
+        <v>-20.90721031496236</v>
       </c>
       <c r="F12">
-        <v>-3.670641073347607</v>
+        <v>-3.669261013254543</v>
       </c>
       <c r="G12">
-        <v>-10.65026782032811</v>
+        <v>-11.12989634751218</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-17.28103630172124</v>
       </c>
       <c r="E13">
-        <v>-20.91185652929423</v>
+        <v>-21.90983710263062</v>
       </c>
       <c r="F13">
-        <v>-3.389036746398512</v>
+        <v>-3.540628809478225</v>
       </c>
       <c r="G13">
-        <v>-10.05193306174239</v>
+        <v>-10.81731463769419</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.60762035658938</v>
       </c>
       <c r="E14">
-        <v>-21.70399531661196</v>
+        <v>-22.12884769106358</v>
       </c>
       <c r="F14">
-        <v>-3.054614885479518</v>
+        <v>-3.814415833247101</v>
       </c>
       <c r="G14">
-        <v>-9.570834652338885</v>
+        <v>-9.595868997706853</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.80959018919295</v>
       </c>
       <c r="E15">
-        <v>-21.51229595491926</v>
+        <v>-22.68986222197783</v>
       </c>
       <c r="F15">
-        <v>-2.624525701578612</v>
+        <v>-3.386120893140658</v>
       </c>
       <c r="G15">
-        <v>-9.387552919648215</v>
+        <v>-9.735636919829345</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.91486877755385</v>
       </c>
       <c r="E16">
-        <v>-22.27667972504398</v>
+        <v>-23.32208247818869</v>
       </c>
       <c r="F16">
-        <v>-2.918093310558938</v>
+        <v>-3.426424280756465</v>
       </c>
       <c r="G16">
-        <v>-8.414381642378517</v>
+        <v>-9.195640594736664</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.98997484991921</v>
       </c>
       <c r="E17">
-        <v>-23.97592166931216</v>
+        <v>-24.99072552358705</v>
       </c>
       <c r="F17">
-        <v>-1.964886798320532</v>
+        <v>-3.144993910961958</v>
       </c>
       <c r="G17">
-        <v>-7.92129243703177</v>
+        <v>-8.856673836970687</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.08332290067415</v>
       </c>
       <c r="E18">
-        <v>-26.78804062943935</v>
+        <v>-24.73590376270143</v>
       </c>
       <c r="F18">
-        <v>-2.070040584799304</v>
+        <v>-3.061630329013827</v>
       </c>
       <c r="G18">
-        <v>-9.505242813569305</v>
+        <v>-8.858041092278405</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.23227859765515</v>
       </c>
       <c r="E19">
-        <v>-26.51449815700602</v>
+        <v>-25.73845809478556</v>
       </c>
       <c r="F19">
-        <v>-2.25501088400742</v>
+        <v>-3.027617563454879</v>
       </c>
       <c r="G19">
-        <v>-8.302134285323989</v>
+        <v>-8.480619037528255</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.49601409002225</v>
       </c>
       <c r="E20">
-        <v>-25.95888156710891</v>
+        <v>-26.8841257909341</v>
       </c>
       <c r="F20">
-        <v>-2.489018048359058</v>
+        <v>-2.628163062844305</v>
       </c>
       <c r="G20">
-        <v>-7.49321903553077</v>
+        <v>-8.975131777456889</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.89766717643512</v>
       </c>
       <c r="E21">
-        <v>-27.53588188401405</v>
+        <v>-27.40375912636626</v>
       </c>
       <c r="F21">
-        <v>-2.030621065202284</v>
+        <v>-2.320270496367368</v>
       </c>
       <c r="G21">
-        <v>-8.070912542679132</v>
+        <v>-8.251026083288719</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.44603408310613</v>
       </c>
       <c r="E22">
-        <v>-27.15315337478178</v>
+        <v>-28.54049214329766</v>
       </c>
       <c r="F22">
-        <v>-2.075972523770751</v>
+        <v>-2.343887251021182</v>
       </c>
       <c r="G22">
-        <v>-7.350713292247303</v>
+        <v>-7.889534373673542</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.16057204671328</v>
       </c>
       <c r="E23">
-        <v>-28.73225943210048</v>
+        <v>-28.09477708909271</v>
       </c>
       <c r="F23">
-        <v>-1.756982319198509</v>
+        <v>-2.154492641514714</v>
       </c>
       <c r="G23">
-        <v>-6.881665268606743</v>
+        <v>-8.47505401047674</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.0252249477308</v>
       </c>
       <c r="E24">
-        <v>-29.25728165160177</v>
+        <v>-29.22790091224</v>
       </c>
       <c r="F24">
-        <v>-1.196338290779387</v>
+        <v>-2.049426661980639</v>
       </c>
       <c r="G24">
-        <v>-6.966044453311687</v>
+        <v>-7.431613093590473</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.01948442866047</v>
       </c>
       <c r="E25">
-        <v>-29.88688671407319</v>
+        <v>-29.38082295100502</v>
       </c>
       <c r="F25">
-        <v>-1.764463305213192</v>
+        <v>-1.94181510941776</v>
       </c>
       <c r="G25">
-        <v>-6.812994622485641</v>
+        <v>-8.465082647312455</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.1318429691654</v>
       </c>
       <c r="E26">
-        <v>-29.18684123841245</v>
+        <v>-29.62255742200847</v>
       </c>
       <c r="F26">
-        <v>-1.319747638081055</v>
+        <v>-1.872914822322509</v>
       </c>
       <c r="G26">
-        <v>-7.646623094729518</v>
+        <v>-7.387950308473025</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.32475910413381</v>
       </c>
       <c r="E27">
-        <v>-28.83896839361722</v>
+        <v>-30.07934006668817</v>
       </c>
       <c r="F27">
-        <v>-1.277219255621328</v>
+        <v>-2.008767076381628</v>
       </c>
       <c r="G27">
-        <v>-7.170752036732521</v>
+        <v>-7.304676845978197</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.57025075500554</v>
       </c>
       <c r="E28">
-        <v>-29.13335543190786</v>
+        <v>-29.83941924952479</v>
       </c>
       <c r="F28">
-        <v>-1.313001413952656</v>
+        <v>-2.191090741737799</v>
       </c>
       <c r="G28">
-        <v>-7.383593630543344</v>
+        <v>-7.850168676666068</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.85288659040348</v>
       </c>
       <c r="E29">
-        <v>-30.8116124276245</v>
+        <v>-29.91404170846019</v>
       </c>
       <c r="F29">
-        <v>-1.661687761547857</v>
+        <v>-1.823022253651895</v>
       </c>
       <c r="G29">
-        <v>-7.32083892930092</v>
+        <v>-7.751011216673818</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.14179995962103</v>
       </c>
       <c r="E30">
-        <v>-30.06286547824827</v>
+        <v>-29.91013137115457</v>
       </c>
       <c r="F30">
-        <v>-1.234029835974168</v>
+        <v>-1.988387581537954</v>
       </c>
       <c r="G30">
-        <v>-6.225432379084712</v>
+        <v>-7.657806117561177</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.42417247540153</v>
       </c>
       <c r="E31">
-        <v>-29.52039504839543</v>
+        <v>-30.72149353063486</v>
       </c>
       <c r="F31">
-        <v>-1.915399301309887</v>
+        <v>-1.966539391289117</v>
       </c>
       <c r="G31">
-        <v>-7.152732737362268</v>
+        <v>-7.827031273892102</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.69838448118862</v>
       </c>
       <c r="E32">
-        <v>-28.6644953470497</v>
+        <v>-30.26898350118139</v>
       </c>
       <c r="F32">
-        <v>-1.536372340852348</v>
+        <v>-1.975440199032198</v>
       </c>
       <c r="G32">
-        <v>-6.892166319057312</v>
+        <v>-7.507510660623804</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.94881677040984</v>
       </c>
       <c r="E33">
-        <v>-29.76831315065635</v>
+        <v>-29.86601271313484</v>
       </c>
       <c r="F33">
-        <v>-1.479785735199711</v>
+        <v>-2.16218486121711</v>
       </c>
       <c r="G33">
-        <v>-6.158910277018597</v>
+        <v>-7.506908141335656</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.18207773388689</v>
       </c>
       <c r="E34">
-        <v>-28.15383744710075</v>
+        <v>-29.33356832473498</v>
       </c>
       <c r="F34">
-        <v>-1.534042143348273</v>
+        <v>-2.060912804387856</v>
       </c>
       <c r="G34">
-        <v>-6.825376062802516</v>
+        <v>-7.515820129927374</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.40962334493361</v>
       </c>
       <c r="E35">
-        <v>-28.71073106666801</v>
+        <v>-29.45184527310432</v>
       </c>
       <c r="F35">
-        <v>-1.560051223061372</v>
+        <v>-2.101131698528578</v>
       </c>
       <c r="G35">
-        <v>-7.862765302442995</v>
+        <v>-7.890252762055564</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-12.62481214751031</v>
       </c>
       <c r="E36">
-        <v>-26.85314197177362</v>
+        <v>-28.41681498967418</v>
       </c>
       <c r="F36">
-        <v>-1.543250275397792</v>
+        <v>-2.228943818576125</v>
       </c>
       <c r="G36">
-        <v>-7.042686893091354</v>
+        <v>-7.319253177987608</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.84446681257479</v>
       </c>
       <c r="E37">
-        <v>-27.86119839977707</v>
+        <v>-28.28004601769452</v>
       </c>
       <c r="F37">
-        <v>-1.928938138141242</v>
+        <v>-2.214322305549311</v>
       </c>
       <c r="G37">
-        <v>-7.382557429789553</v>
+        <v>-7.566140422124296</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.07970864846896</v>
       </c>
       <c r="E38">
-        <v>-26.58501102577945</v>
+        <v>-27.89573254255956</v>
       </c>
       <c r="F38">
-        <v>-1.247045972974356</v>
+        <v>-2.236363505403</v>
       </c>
       <c r="G38">
-        <v>-7.363210601658052</v>
+        <v>-7.712393702958219</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.31865361770688</v>
       </c>
       <c r="E39">
-        <v>-27.20067970949228</v>
+        <v>-27.39032767245951</v>
       </c>
       <c r="F39">
-        <v>-1.30413456927309</v>
+        <v>-2.097639301558376</v>
       </c>
       <c r="G39">
-        <v>-7.000537027285354</v>
+        <v>-6.8974002915549</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.57583108755063</v>
       </c>
       <c r="E40">
-        <v>-26.52602312335554</v>
+        <v>-27.02501114578673</v>
       </c>
       <c r="F40">
-        <v>-1.512584942513557</v>
+        <v>-2.137445668732503</v>
       </c>
       <c r="G40">
-        <v>-6.441677213709906</v>
+        <v>-7.414716069158032</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.85027071372609</v>
       </c>
       <c r="E41">
-        <v>-25.41716286394135</v>
+        <v>-27.04160800302484</v>
       </c>
       <c r="F41">
-        <v>-1.542448415751882</v>
+        <v>-2.202303522902093</v>
       </c>
       <c r="G41">
-        <v>-6.456081397351275</v>
+        <v>-7.098171636329539</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-14.11859439686227</v>
       </c>
       <c r="E42">
-        <v>-26.55815717491397</v>
+        <v>-26.72138149204644</v>
       </c>
       <c r="F42">
-        <v>-1.441222747497186</v>
+        <v>-2.389337285310582</v>
       </c>
       <c r="G42">
-        <v>-6.876222731740182</v>
+        <v>-7.583239389834632</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-14.38714649965</v>
       </c>
       <c r="E43">
-        <v>-25.29264794262644</v>
+        <v>-26.99721537232765</v>
       </c>
       <c r="F43">
-        <v>-1.446079465579799</v>
+        <v>-2.045561499679176</v>
       </c>
       <c r="G43">
-        <v>-6.879013521629787</v>
+        <v>-6.937080490388603</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-14.64424023289039</v>
       </c>
       <c r="E44">
-        <v>-24.25996567296928</v>
+        <v>-24.36697351377053</v>
       </c>
       <c r="F44">
-        <v>-1.762561373656364</v>
+        <v>-2.40340379217752</v>
       </c>
       <c r="G44">
-        <v>-7.53596479953384</v>
+        <v>-6.892067002691133</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.86606383754785</v>
       </c>
       <c r="E45">
-        <v>-24.22825276949357</v>
+        <v>-24.52897514292093</v>
       </c>
       <c r="F45">
-        <v>-1.376371520266818</v>
+        <v>-2.037941347940823</v>
       </c>
       <c r="G45">
-        <v>-7.035943311827859</v>
+        <v>-7.647728816939635</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-15.06058241871276</v>
       </c>
       <c r="E46">
-        <v>-24.61169224914504</v>
+        <v>-24.78917220245365</v>
       </c>
       <c r="F46">
-        <v>-1.141137543791634</v>
+        <v>-1.824955663170029</v>
       </c>
       <c r="G46">
-        <v>-7.841402352078078</v>
+        <v>-7.046695963739412</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-15.2166837628326</v>
       </c>
       <c r="E47">
-        <v>-23.82495140284445</v>
+        <v>-23.68145311848939</v>
       </c>
       <c r="F47">
-        <v>-1.411606127744895</v>
+        <v>-1.727322624341273</v>
       </c>
       <c r="G47">
-        <v>-6.911036428631157</v>
+        <v>-7.345535599023883</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-15.32128228228319</v>
       </c>
       <c r="E48">
-        <v>-22.69425484176527</v>
+        <v>-22.99132726514245</v>
       </c>
       <c r="F48">
-        <v>-1.39211381438962</v>
+        <v>-2.27247783906285</v>
       </c>
       <c r="G48">
-        <v>-7.250721574779156</v>
+        <v>-7.462613042020208</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-15.38816118601348</v>
       </c>
       <c r="E49">
-        <v>-21.39717308869626</v>
+        <v>-23.26959293596578</v>
       </c>
       <c r="F49">
-        <v>-1.384677560214689</v>
+        <v>-2.105873273542203</v>
       </c>
       <c r="G49">
-        <v>-7.331157899746827</v>
+        <v>-7.63721452430691</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-15.41200945375477</v>
       </c>
       <c r="E50">
-        <v>-22.40493063741521</v>
+        <v>-22.50324833659574</v>
       </c>
       <c r="F50">
-        <v>-1.970845245048869</v>
+        <v>-2.050886245344371</v>
       </c>
       <c r="G50">
-        <v>-7.161972469962373</v>
+        <v>-7.644491103402228</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-15.39217964581969</v>
       </c>
       <c r="E51">
-        <v>-20.91332375487272</v>
+        <v>-21.793165498297</v>
       </c>
       <c r="F51">
-        <v>-1.382174233923428</v>
+        <v>-2.220178863087103</v>
       </c>
       <c r="G51">
-        <v>-6.206400052779442</v>
+        <v>-7.84761624605529</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-15.34579106414493</v>
       </c>
       <c r="E52">
-        <v>-20.96070517841497</v>
+        <v>-21.8875705959349</v>
       </c>
       <c r="F52">
-        <v>-1.674224273821825</v>
+        <v>-2.412587073204956</v>
       </c>
       <c r="G52">
-        <v>-7.907954249054047</v>
+        <v>-7.768984168406521</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-15.26696361567536</v>
       </c>
       <c r="E53">
-        <v>-20.84104025276228</v>
+        <v>-21.14534012065571</v>
       </c>
       <c r="F53">
-        <v>-1.810803834460602</v>
+        <v>-2.063495653949786</v>
       </c>
       <c r="G53">
-        <v>-7.626455251304279</v>
+        <v>-8.28359191975853</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-15.15926559264984</v>
       </c>
       <c r="E54">
-        <v>-20.71487243843458</v>
+        <v>-20.61169115816981</v>
       </c>
       <c r="F54">
-        <v>-1.961475581355804</v>
+        <v>-1.98471708557615</v>
       </c>
       <c r="G54">
-        <v>-7.609975355609786</v>
+        <v>-8.632179122861629</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-15.03537405491764</v>
       </c>
       <c r="E55">
-        <v>-19.90967806055274</v>
+        <v>-20.37878268300731</v>
       </c>
       <c r="F55">
-        <v>-1.41923290642247</v>
+        <v>-2.211126464109311</v>
       </c>
       <c r="G55">
-        <v>-8.873157043210718</v>
+        <v>-8.43031529805903</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-14.88553162883879</v>
       </c>
       <c r="E56">
-        <v>-18.71418809337181</v>
+        <v>-19.88180077456152</v>
       </c>
       <c r="F56">
-        <v>-2.081315493518809</v>
+        <v>-1.808127379382157</v>
       </c>
       <c r="G56">
-        <v>-6.900545309817207</v>
+        <v>-8.284439419416584</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.717907528765</v>
       </c>
       <c r="E57">
-        <v>-18.20058668531787</v>
+        <v>-20.36067784392464</v>
       </c>
       <c r="F57">
-        <v>-1.993921075788655</v>
+        <v>-2.323933537022547</v>
       </c>
       <c r="G57">
-        <v>-8.071584583423604</v>
+        <v>-8.732564795248949</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.54247937841166</v>
       </c>
       <c r="E58">
-        <v>-19.23830008959755</v>
+        <v>-18.81895886801327</v>
       </c>
       <c r="F58">
-        <v>-1.124216482854648</v>
+        <v>-2.155425383210266</v>
       </c>
       <c r="G58">
-        <v>-8.263801478524767</v>
+        <v>-8.908728855030187</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.34747671111518</v>
       </c>
       <c r="E59">
-        <v>-18.41673074970397</v>
+        <v>-19.34900769366307</v>
       </c>
       <c r="F59">
-        <v>-1.975953786821934</v>
+        <v>-2.038591616352021</v>
       </c>
       <c r="G59">
-        <v>-8.28286691028543</v>
+        <v>-8.476590103606963</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.14573791682949</v>
       </c>
       <c r="E60">
-        <v>-16.72575779897379</v>
+        <v>-18.41736020759104</v>
       </c>
       <c r="F60">
-        <v>-1.767712990534374</v>
+        <v>-2.308856421924193</v>
       </c>
       <c r="G60">
-        <v>-8.031742167858475</v>
+        <v>-8.196961564086882</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.94412559975082</v>
       </c>
       <c r="E61">
-        <v>-17.01254152940555</v>
+        <v>-18.20081763749226</v>
       </c>
       <c r="F61">
-        <v>-1.525413040113311</v>
+        <v>-2.441357929838988</v>
       </c>
       <c r="G61">
-        <v>-7.897714731701081</v>
+        <v>-8.556112718005796</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.72834946583522</v>
       </c>
       <c r="E62">
-        <v>-17.0561416771514</v>
+        <v>-17.99596305880727</v>
       </c>
       <c r="F62">
-        <v>-1.477414119325496</v>
+        <v>-2.505317005376541</v>
       </c>
       <c r="G62">
-        <v>-8.506500882554278</v>
+        <v>-8.639319969589838</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.51383059738664</v>
       </c>
       <c r="E63">
-        <v>-16.88943043503302</v>
+        <v>-18.08309089871485</v>
       </c>
       <c r="F63">
-        <v>-2.231368449964119</v>
+        <v>-2.310267959978564</v>
       </c>
       <c r="G63">
-        <v>-8.996458311820874</v>
+        <v>-9.127314245351647</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.30195834888184</v>
       </c>
       <c r="E64">
-        <v>-16.86822811972911</v>
+        <v>-17.5425631842113</v>
       </c>
       <c r="F64">
-        <v>-2.20019284275976</v>
+        <v>-2.209332220314847</v>
       </c>
       <c r="G64">
-        <v>-8.825667267449873</v>
+        <v>-8.724371195039254</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.07691734296167</v>
       </c>
       <c r="E65">
-        <v>-16.27790530503722</v>
+        <v>-17.29947469947956</v>
       </c>
       <c r="F65">
-        <v>-1.546924913196611</v>
+        <v>-2.537721909806655</v>
       </c>
       <c r="G65">
-        <v>-7.46451329515975</v>
+        <v>-9.251426597618924</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.85360738831468</v>
       </c>
       <c r="E66">
-        <v>-16.32266021365502</v>
+        <v>-16.64247463349873</v>
       </c>
       <c r="F66">
-        <v>-1.78626759198968</v>
+        <v>-2.320264697795548</v>
       </c>
       <c r="G66">
-        <v>-8.899869835167097</v>
+        <v>-8.694443863364242</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.62873683484368</v>
       </c>
       <c r="E67">
-        <v>-15.85236913101044</v>
+        <v>-17.1257488511233</v>
       </c>
       <c r="F67">
-        <v>-2.073048386838869</v>
+        <v>-2.653639502317404</v>
       </c>
       <c r="G67">
-        <v>-8.372936922772382</v>
+        <v>-9.462434149200989</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.38814559175692</v>
       </c>
       <c r="E68">
-        <v>-17.39379375611131</v>
+        <v>-17.16241590516341</v>
       </c>
       <c r="F68">
-        <v>-2.477930350672586</v>
+        <v>-2.459208419001915</v>
       </c>
       <c r="G68">
-        <v>-8.773079251558551</v>
+        <v>-9.32952236689033</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.14577436337622</v>
       </c>
       <c r="E69">
-        <v>-16.9295029015269</v>
+        <v>-16.63061456007264</v>
       </c>
       <c r="F69">
-        <v>-1.822362044831863</v>
+        <v>-2.516456890209389</v>
       </c>
       <c r="G69">
-        <v>-8.091868295942719</v>
+        <v>-8.845603372687364</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.89609553774479</v>
       </c>
       <c r="E70">
-        <v>-15.71495711572169</v>
+        <v>-15.96824825239272</v>
       </c>
       <c r="F70">
-        <v>-2.175598614570642</v>
+        <v>-2.215554916244677</v>
       </c>
       <c r="G70">
-        <v>-8.38870836172147</v>
+        <v>-9.224005348917139</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.63023947353863</v>
       </c>
       <c r="E71">
-        <v>-16.33156772202811</v>
+        <v>-17.61213865886515</v>
       </c>
       <c r="F71">
-        <v>-1.625806199128194</v>
+        <v>-2.772144914594498</v>
       </c>
       <c r="G71">
-        <v>-8.722838412454571</v>
+        <v>-9.751269315865782</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.36196035335052</v>
       </c>
       <c r="E72">
-        <v>-14.55824447146844</v>
+        <v>-16.95475367259366</v>
       </c>
       <c r="F72">
-        <v>-2.187473261289774</v>
+        <v>-2.372760825213161</v>
       </c>
       <c r="G72">
-        <v>-8.639372938318466</v>
+        <v>-9.542668530890767</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.08662833378223</v>
       </c>
       <c r="E73">
-        <v>-17.45840149477875</v>
+        <v>-17.56749696209753</v>
       </c>
       <c r="F73">
-        <v>-2.114257180025936</v>
+        <v>-2.493155743536041</v>
       </c>
       <c r="G73">
-        <v>-8.253320291347436</v>
+        <v>-8.760446209780692</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.8026145238583</v>
       </c>
       <c r="E74">
-        <v>-17.5505332984648</v>
+        <v>-16.85300791858933</v>
       </c>
       <c r="F74">
-        <v>-1.918449350086995</v>
+        <v>-2.646348212437962</v>
       </c>
       <c r="G74">
-        <v>-9.00288077016706</v>
+        <v>-9.184490677360399</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.52303307949031</v>
       </c>
       <c r="E75">
-        <v>-18.3846283974636</v>
+        <v>-17.2703928394023</v>
       </c>
       <c r="F75">
-        <v>-1.893421057378811</v>
+        <v>-2.732144709448116</v>
       </c>
       <c r="G75">
-        <v>-8.376737429051465</v>
+        <v>-8.846288655613993</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.24321823995573</v>
       </c>
       <c r="E76">
-        <v>-17.46848187791982</v>
+        <v>-17.61672147456091</v>
       </c>
       <c r="F76">
-        <v>-2.054660287231526</v>
+        <v>-2.813726473112825</v>
       </c>
       <c r="G76">
-        <v>-8.489838906855125</v>
+        <v>-9.038363197256968</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.965486943965471</v>
       </c>
       <c r="E77">
-        <v>-16.83757487917119</v>
+        <v>-18.26842322595277</v>
       </c>
       <c r="F77">
-        <v>-2.547557115980093</v>
+        <v>-2.84121087517031</v>
       </c>
       <c r="G77">
-        <v>-7.197557523964</v>
+        <v>-8.425955309583809</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.700079822995676</v>
       </c>
       <c r="E78">
-        <v>-18.18046667530179</v>
+        <v>-18.58015884816679</v>
       </c>
       <c r="F78">
-        <v>-2.911653582369574</v>
+        <v>-2.965059257195461</v>
       </c>
       <c r="G78">
-        <v>-8.381882016819493</v>
+        <v>-9.059802290169289</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.440495409843942</v>
       </c>
       <c r="E79">
-        <v>-18.02050738792884</v>
+        <v>-18.21706127375777</v>
       </c>
       <c r="F79">
-        <v>-2.275294288232369</v>
+        <v>-2.864536044498338</v>
       </c>
       <c r="G79">
-        <v>-7.830242503065195</v>
+        <v>-8.624396030298803</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.191169695239257</v>
       </c>
       <c r="E80">
-        <v>-17.98649854813124</v>
+        <v>-19.03858985738528</v>
       </c>
       <c r="F80">
-        <v>-2.548096383159316</v>
+        <v>-3.190206203806755</v>
       </c>
       <c r="G80">
-        <v>-7.800623052125336</v>
+        <v>-8.147038537354673</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.95926883751472</v>
       </c>
       <c r="E81">
-        <v>-18.04841637323812</v>
+        <v>-19.55850395820591</v>
       </c>
       <c r="F81">
-        <v>-2.803378507517054</v>
+        <v>-2.998765526815373</v>
       </c>
       <c r="G81">
-        <v>-8.211309468454083</v>
+        <v>-8.098846925939501</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.736761527496409</v>
       </c>
       <c r="E82">
-        <v>-18.94809283281599</v>
+        <v>-19.95364954316721</v>
       </c>
       <c r="F82">
-        <v>-2.833119382379764</v>
+        <v>-2.884879091176288</v>
       </c>
       <c r="G82">
-        <v>-8.180230066931406</v>
+        <v>-9.134792767724859</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.530831616196776</v>
       </c>
       <c r="E83">
-        <v>-19.78739567692361</v>
+        <v>-21.65628331446715</v>
       </c>
       <c r="F83">
-        <v>-2.916486277797506</v>
+        <v>-3.193510561376522</v>
       </c>
       <c r="G83">
-        <v>-7.40355290959961</v>
+        <v>-8.053664600419529</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.348187909060604</v>
       </c>
       <c r="E84">
-        <v>-20.55319233093872</v>
+        <v>-21.25514202991969</v>
       </c>
       <c r="F84">
-        <v>-2.382828802626786</v>
+        <v>-3.075749023027142</v>
       </c>
       <c r="G84">
-        <v>-7.159181680072768</v>
+        <v>-8.380812710610307</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.181875179079174</v>
       </c>
       <c r="E85">
-        <v>-23.09781433143282</v>
+        <v>-22.41099879258549</v>
       </c>
       <c r="F85">
-        <v>-2.399710101928437</v>
+        <v>-3.106410214074363</v>
       </c>
       <c r="G85">
-        <v>-7.044222986221576</v>
+        <v>-8.437691193520525</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.044318802543939</v>
       </c>
       <c r="E86">
-        <v>-23.33114395467803</v>
+        <v>-23.62142819551772</v>
       </c>
       <c r="F86">
-        <v>-2.685782642648233</v>
+        <v>-3.401698342150303</v>
       </c>
       <c r="G86">
-        <v>-8.57803184002131</v>
+        <v>-8.501578101337381</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.944641075652729</v>
       </c>
       <c r="E87">
-        <v>-23.39839632216595</v>
+        <v>-24.64253115713727</v>
       </c>
       <c r="F87">
-        <v>-2.730029059101366</v>
+        <v>-3.266903913264559</v>
       </c>
       <c r="G87">
-        <v>-7.718994930763526</v>
+        <v>-8.540897450707305</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.877894243637783</v>
       </c>
       <c r="E88">
-        <v>-24.46721581440432</v>
+        <v>-25.15350605026676</v>
       </c>
       <c r="F88">
-        <v>-2.662175828403253</v>
+        <v>-3.711317226294674</v>
       </c>
       <c r="G88">
-        <v>-6.51742580619397</v>
+        <v>-8.778462198605405</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.861857944549912</v>
       </c>
       <c r="E89">
-        <v>-26.46990174497848</v>
+        <v>-26.79384613311718</v>
       </c>
       <c r="F89">
-        <v>-2.805904199728189</v>
+        <v>-3.75536649130594</v>
       </c>
       <c r="G89">
-        <v>-7.08481689562412</v>
+        <v>-8.442895371108261</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.905376127280779</v>
       </c>
       <c r="E90">
-        <v>-27.7057675864118</v>
+        <v>-28.03716584276712</v>
       </c>
       <c r="F90">
-        <v>-3.026636776449965</v>
+        <v>-3.440543803137183</v>
       </c>
       <c r="G90">
-        <v>-9.250800904512001</v>
+        <v>-8.842147163144364</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.002512465136606</v>
       </c>
       <c r="E91">
-        <v>-30.2397069167218</v>
+        <v>-29.10211801820295</v>
       </c>
       <c r="F91">
-        <v>-3.532597787508084</v>
+        <v>-3.332811308933496</v>
       </c>
       <c r="G91">
-        <v>-9.058901821782607</v>
+        <v>-8.731525283949619</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.168873817540312</v>
       </c>
       <c r="E92">
-        <v>-30.82816626435954</v>
+        <v>-30.84405441541545</v>
       </c>
       <c r="F92">
-        <v>-3.450346702981912</v>
+        <v>-3.794766130085293</v>
       </c>
       <c r="G92">
-        <v>-9.823078359158114</v>
+        <v>-9.525496731178567</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.405778924856529</v>
       </c>
       <c r="E93">
-        <v>-31.7505643422709</v>
+        <v>-32.87483952720721</v>
       </c>
       <c r="F93">
-        <v>-2.944246526200123</v>
+        <v>-3.436189904068069</v>
       </c>
       <c r="G93">
-        <v>-8.770295082760024</v>
+        <v>-9.019244796767678</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.698456534889754</v>
       </c>
       <c r="E94">
-        <v>-34.30670678064051</v>
+        <v>-34.06703955802156</v>
       </c>
       <c r="F94">
-        <v>-3.047768428895381</v>
+        <v>-3.447566701978117</v>
       </c>
       <c r="G94">
-        <v>-8.775767414536439</v>
+        <v>-9.171473612299984</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.051401631920614</v>
       </c>
       <c r="E95">
-        <v>-36.00997227406452</v>
+        <v>-36.33189017008478</v>
       </c>
       <c r="F95">
-        <v>-2.443312876909595</v>
+        <v>-3.428762761934568</v>
       </c>
       <c r="G95">
-        <v>-8.415729034413001</v>
+        <v>-8.855892548223419</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.451430121739062</v>
       </c>
       <c r="E96">
-        <v>-36.85449192022897</v>
+        <v>-38.22091593154042</v>
       </c>
       <c r="F96">
-        <v>-3.24162296849852</v>
+        <v>-3.644037225839298</v>
       </c>
       <c r="G96">
-        <v>-8.233784762120196</v>
+        <v>-9.5797631936583</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.869906490173801</v>
       </c>
       <c r="E97">
-        <v>-38.04762934516291</v>
+        <v>-39.76202809193477</v>
       </c>
       <c r="F97">
-        <v>-3.189213819658201</v>
+        <v>-3.391396765129088</v>
       </c>
       <c r="G97">
-        <v>-9.105987710987661</v>
+        <v>-9.688643725899389</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.30232114836738</v>
       </c>
       <c r="E98">
-        <v>-41.64095535635331</v>
+        <v>-41.97297174941068</v>
       </c>
       <c r="F98">
-        <v>-3.115494091013463</v>
+        <v>-3.340356907605597</v>
       </c>
       <c r="G98">
-        <v>-8.544085506061624</v>
+        <v>-9.854896012336051</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.71634805349335</v>
       </c>
       <c r="E99">
-        <v>-43.63494661683274</v>
+        <v>-44.11138283870573</v>
       </c>
       <c r="F99">
-        <v>-3.595349103372354</v>
+        <v>-3.372121484033346</v>
       </c>
       <c r="G99">
-        <v>-9.397838784638731</v>
+        <v>-10.17313213393511</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.09646971954935</v>
       </c>
       <c r="E100">
-        <v>-45.16787808893223</v>
+        <v>-45.88998402572134</v>
       </c>
       <c r="F100">
-        <v>-3.099649079332714</v>
+        <v>-3.751078033261647</v>
       </c>
       <c r="G100">
-        <v>-9.233043138239349</v>
+        <v>-9.920021064184592</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.4168107605329</v>
       </c>
       <c r="E101">
-        <v>-48.60098216125724</v>
+        <v>-48.02601766616237</v>
       </c>
       <c r="F101">
-        <v>-3.185381792052851</v>
+        <v>-3.56621376508109</v>
       </c>
       <c r="G101">
-        <v>-8.848086281841818</v>
+        <v>-10.80059969326641</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.68833874131275</v>
       </c>
       <c r="E102">
-        <v>-49.82092702019809</v>
+        <v>-50.00942588288588</v>
       </c>
       <c r="F102">
-        <v>-3.033258745467944</v>
+        <v>-3.632739122832516</v>
       </c>
       <c r="G102">
-        <v>-9.066367101973663</v>
+        <v>-9.794865890072446</v>
       </c>
     </row>
   </sheetData>
